--- a/Collections/Russia/#Russia#Russian_Empire#Regular#[1867-1917]#circulation_quality.xlsx
+++ b/Collections/Russia/#Russia#Russian_Empire#Regular#[1867-1917]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Russia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EDCC95D-54E4-484E-B359-129A863EE7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AACE4E3-F4D4-4F1E-A894-967052638EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="2510" windowWidth="33150" windowHeight="17700" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="¼ копейки" sheetId="1" r:id="rId1"/>
@@ -22,20 +22,20 @@
     <sheet name="10 копеек" sheetId="22" r:id="rId7"/>
     <sheet name="15 копеек" sheetId="23" r:id="rId8"/>
     <sheet name="20 копеек" sheetId="24" r:id="rId9"/>
-    <sheet name="Лист7" sheetId="20" r:id="rId10"/>
+    <sheet name="1 рубль" sheetId="25" r:id="rId10"/>
     <sheet name="Links" sheetId="10" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'¼ копейки'!$B$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'½ копейки'!$B$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1 копейка'!$B$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'1 рубль'!$B$2:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'10 копеек'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'15 копеек'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2 копейки'!$B$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'20 копеек'!$B$2:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3 копейки'!$B$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5 копеек'!$B$2:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Лист7!$F$4:$K$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -118,6 +118,110 @@
             <charset val="204"/>
           </rPr>
           <t>Saint Petersburg Mint</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Пользователь Windows</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{60687423-1DE5-448C-95A5-4B3E24ADC44B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Saint Petersburg Mint</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{006AA91F-2B78-4230-9E65-FA8106018C51}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Monnaie royale de Belgique
+ (Belgium mint)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{66792510-FFC2-4C2A-83BA-C06F301ECD2F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Monnaie de Paris
+(Paris mint)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{C736D75B-6585-45A2-BE70-A7BD26C1997B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Saint Petersburg Mint</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{D5C0DFAE-FC99-4310-88C0-F38165F36AFD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Monnaie royale de Belgique
+ (Belgium mint)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{DD8FB36D-3EC4-4417-8AC1-574099282895}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Monnaie de Paris
+(Paris mint)</t>
         </r>
       </text>
     </comment>
@@ -596,7 +700,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="453">
   <si>
     <t>-</t>
   </si>
@@ -1384,18 +1488,12 @@
     <t>Obv: Mintmaster inicials - "HI"</t>
   </si>
   <si>
-    <t>ВС</t>
-  </si>
-  <si>
     <t>3.000.000</t>
   </si>
   <si>
     <t>4.200.000</t>
   </si>
   <si>
-    <t>+</t>
-  </si>
-  <si>
     <t>1.300.000</t>
   </si>
   <si>
@@ -1405,27 +1503,15 @@
     <t>3.100.000</t>
   </si>
   <si>
-    <t>СПБ АР</t>
-  </si>
-  <si>
-    <t>СПБ ФЗ</t>
-  </si>
-  <si>
     <t>5.790.000</t>
   </si>
   <si>
     <t>4.003.009</t>
   </si>
   <si>
-    <t>СПБ АГ</t>
-  </si>
-  <si>
     <t>4.605.022</t>
   </si>
   <si>
-    <t>СПБ ЭБ</t>
-  </si>
-  <si>
     <t>3.980.009</t>
   </si>
   <si>
@@ -1456,15 +1542,9 @@
     <t>1.800.026</t>
   </si>
   <si>
-    <t>СПБ ДС</t>
-  </si>
-  <si>
     <t>960.008</t>
   </si>
   <si>
-    <t>СПБ НФ</t>
-  </si>
-  <si>
     <t>1.860.207</t>
   </si>
   <si>
@@ -1477,9 +1557,6 @@
     <t>140.005</t>
   </si>
   <si>
-    <t>СПБ НI</t>
-  </si>
-  <si>
     <t>220.006</t>
   </si>
   <si>
@@ -1507,9 +1584,6 @@
     <t>180.025</t>
   </si>
   <si>
-    <t>$ 57</t>
-  </si>
-  <si>
     <t>Obv: Mintmaster inicials - "НФ"</t>
   </si>
   <si>
@@ -1603,9 +1677,6 @@
     <t>82.500.000</t>
   </si>
   <si>
-    <t>СПБ ВС</t>
-  </si>
-  <si>
     <t>51.250.000</t>
   </si>
   <si>
@@ -1711,12 +1782,6 @@
     <t>6.445.092</t>
   </si>
   <si>
-    <t>$ 4,13</t>
-  </si>
-  <si>
-    <t>$ 4,9</t>
-  </si>
-  <si>
     <t>10 копеек</t>
   </si>
   <si>
@@ -1858,24 +1923,6 @@
     <t>8.720.011</t>
   </si>
   <si>
-    <t>$ 5,49</t>
-  </si>
-  <si>
-    <t>$ 5,43</t>
-  </si>
-  <si>
-    <t>$ 4,52</t>
-  </si>
-  <si>
-    <t>$ 4,37</t>
-  </si>
-  <si>
-    <t>$ 4,98</t>
-  </si>
-  <si>
-    <t>$ 5,55</t>
-  </si>
-  <si>
     <t>3.500.000</t>
   </si>
   <si>
@@ -1981,121 +2028,37 @@
     <t>15.335.071</t>
   </si>
   <si>
-    <t>$ 572</t>
-  </si>
-  <si>
-    <t>$ 6,79</t>
-  </si>
-  <si>
-    <t>$ 6,26</t>
-  </si>
-  <si>
-    <t>$ 4,62</t>
-  </si>
-  <si>
-    <t>$ 5,17</t>
-  </si>
-  <si>
-    <t>$ 6,06</t>
-  </si>
-  <si>
-    <t>$ 5,79</t>
-  </si>
-  <si>
-    <t>$ 6,01</t>
-  </si>
-  <si>
-    <t>$ 6,21</t>
-  </si>
-  <si>
-    <t>$ 5,26</t>
-  </si>
-  <si>
-    <t>$ 4,75</t>
-  </si>
-  <si>
-    <t>$ 8,86</t>
-  </si>
-  <si>
-    <t>$ 5,36</t>
-  </si>
-  <si>
-    <t>$ 4,3</t>
-  </si>
-  <si>
-    <t>$ 4,73</t>
-  </si>
-  <si>
-    <t>$ 7,35</t>
-  </si>
-  <si>
-    <t>$ 7,92</t>
-  </si>
-  <si>
-    <t>$ 4,53</t>
-  </si>
-  <si>
-    <t>$ 8,38</t>
-  </si>
-  <si>
-    <t>$ 8,85</t>
-  </si>
-  <si>
-    <t>$ 11,05</t>
-  </si>
-  <si>
-    <t>$ 8,97</t>
-  </si>
-  <si>
-    <t>$ 11,97</t>
-  </si>
-  <si>
-    <t>$ 8,62</t>
-  </si>
-  <si>
-    <t>$ 10,99</t>
-  </si>
-  <si>
-    <t>$ 5,51</t>
-  </si>
-  <si>
-    <t>$ 4,59</t>
-  </si>
-  <si>
-    <t>$ 5,32</t>
-  </si>
-  <si>
-    <t>$ 7,64</t>
-  </si>
-  <si>
-    <t>$ 5,86</t>
-  </si>
-  <si>
-    <t>$ 9,32</t>
-  </si>
-  <si>
-    <t>$ 7,05</t>
-  </si>
-  <si>
-    <t>$ 6,02</t>
-  </si>
-  <si>
-    <t>$ 5,25</t>
-  </si>
-  <si>
-    <t>$ 7,6</t>
-  </si>
-  <si>
-    <t>$ 4,76</t>
-  </si>
-  <si>
-    <t>$ 4,22</t>
-  </si>
-  <si>
-    <t>$ 5,2</t>
-  </si>
-  <si>
     <t>20 копеек</t>
+  </si>
+  <si>
+    <t>1 рубль</t>
+  </si>
+  <si>
+    <t>25.877.842</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>#Edge</t>
+  </si>
+  <si>
+    <t>Silver (0.900)</t>
+  </si>
+  <si>
+    <t>Obv: Portrait of the Emperor Nicholas II</t>
+  </si>
+  <si>
+    <t>Legend at edge - "*"</t>
+  </si>
+  <si>
+    <t>Legend at edge - "**"</t>
+  </si>
+  <si>
+    <t>Legend at edge - "А.Г."/ Appolon Grasgov - Chief of the Saint Petersburg Mint</t>
   </si>
 </sst>
 </file>
@@ -2204,7 +2167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2290,13 +2253,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2382,6 +2385,9 @@
     <xf numFmtId="3" fontId="7" fillId="7" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2404,13 +2410,204 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="218">
+  <dxfs count="240">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4261,6 +4458,65 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44860F36-5342-47D6-8CEF-1704B364E333}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10648950" y="0"/>
+          <a:ext cx="609600" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -4741,9 +4997,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="217"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="216" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="215"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="239"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="238" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="237"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5059,26 +5315,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="23"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="31" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37" t="s">
+      <c r="G1" s="37"/>
+      <c r="H1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="38"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -6725,7 +6981,7 @@
     <mergeCell ref="H1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="H3 H13:I18 H20:I31">
-    <cfRule type="containsText" dxfId="214" priority="62" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="236" priority="62" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6742,7 +6998,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:I7">
-    <cfRule type="containsText" dxfId="213" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="235" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6759,7 +7015,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H47:I47">
-    <cfRule type="containsText" dxfId="212" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="234" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6776,7 +7032,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:I33">
-    <cfRule type="containsText" dxfId="211" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="233" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6793,7 +7049,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:I34">
-    <cfRule type="containsText" dxfId="210" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="232" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6810,7 +7066,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I4">
-    <cfRule type="containsText" dxfId="209" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="231" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6827,7 +7083,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="208" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="230" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6844,7 +7100,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:I12">
-    <cfRule type="containsText" dxfId="207" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="229" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6861,7 +7117,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:I38">
-    <cfRule type="containsText" dxfId="206" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="228" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6878,7 +7134,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H12">
-    <cfRule type="containsText" dxfId="205" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="227" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6895,7 +7151,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:I48">
-    <cfRule type="containsText" dxfId="204" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="226" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H48))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6912,7 +7168,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="203" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="225" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6929,7 +7185,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54:I54">
-    <cfRule type="containsText" dxfId="202" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="224" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6946,7 +7202,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:I19">
-    <cfRule type="containsText" dxfId="201" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="223" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6963,7 +7219,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:I32">
-    <cfRule type="containsText" dxfId="200" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="222" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6980,7 +7236,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35">
-    <cfRule type="containsText" dxfId="199" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="221" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6997,7 +7253,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H36:I36">
-    <cfRule type="containsText" dxfId="198" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="220" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7014,7 +7270,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:I37">
-    <cfRule type="containsText" dxfId="197" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="219" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7031,7 +7287,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H53:I53">
-    <cfRule type="containsText" dxfId="196" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="218" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H53))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7055,1103 +7311,336 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E02B6B0-E213-4BD1-B779-1B5FAA895902}">
-  <dimension ref="F3:K86"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02AF99F0-2951-4CDD-B3E0-7A8779F916A1}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.6328125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="50.6328125" style="10" customWidth="1"/>
+    <col min="3" max="4" width="33.6328125" style="3" customWidth="1"/>
+    <col min="5" max="7" width="12.6328125" style="11" customWidth="1"/>
+    <col min="8" max="10" width="3.6328125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.6328125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F5">
-        <v>1867</v>
-      </c>
-      <c r="G5" t="s">
-        <v>293</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>460</v>
-      </c>
-      <c r="I5" t="s">
-        <v>265</v>
-      </c>
-      <c r="J5" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F6">
-        <v>1868</v>
-      </c>
-      <c r="G6" t="s">
-        <v>293</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="I6" t="s">
-        <v>265</v>
-      </c>
-      <c r="J6" t="s">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="7" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F7">
-        <v>1869</v>
-      </c>
-      <c r="G7" t="s">
-        <v>293</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="I7" t="s">
-        <v>265</v>
-      </c>
-      <c r="J7" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="8" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F8">
-        <v>1870</v>
-      </c>
-      <c r="G8" t="s">
-        <v>293</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>457</v>
-      </c>
-      <c r="I8" t="s">
-        <v>265</v>
-      </c>
-      <c r="J8" t="s">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="9" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F9">
-        <v>1871</v>
-      </c>
-      <c r="G9" t="s">
-        <v>293</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>456</v>
-      </c>
-      <c r="I9" t="s">
-        <v>265</v>
-      </c>
-      <c r="J9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="10" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F10">
-        <v>1872</v>
-      </c>
-      <c r="G10" t="s">
-        <v>293</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="I10" t="s">
-        <v>265</v>
-      </c>
-      <c r="J10" t="s">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="11" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F11">
-        <v>1873</v>
-      </c>
-      <c r="G11" t="s">
-        <v>293</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>454</v>
-      </c>
-      <c r="I11" t="s">
-        <v>265</v>
-      </c>
-      <c r="J11" t="s">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="12" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F12">
-        <v>1874</v>
-      </c>
-      <c r="G12" t="s">
-        <v>293</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="I12" t="s">
-        <v>265</v>
-      </c>
-      <c r="J12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="13" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F13">
-        <v>1875</v>
-      </c>
-      <c r="G13" t="s">
-        <v>293</v>
-      </c>
-      <c r="H13" s="14" t="s">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="34"/>
+      <c r="E1" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="40" t="s">
+        <v>443</v>
+      </c>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1"/>
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="36"/>
+      <c r="B2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="K2"/>
+    </row>
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>1898</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="I13" t="s">
-        <v>265</v>
-      </c>
-      <c r="J13" t="s">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="14" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F14">
-        <v>1876</v>
-      </c>
-      <c r="G14" t="s">
-        <v>293</v>
-      </c>
-      <c r="H14" s="14" t="s">
+      <c r="E3" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="str">
+        <f>IF(OR(AND(H3&gt;1,H3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>1898</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="I14" t="s">
-        <v>265</v>
-      </c>
-      <c r="J14" t="s">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="15" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F15">
-        <v>1877</v>
-      </c>
-      <c r="G15" t="s">
-        <v>293</v>
-      </c>
-      <c r="H15" s="14" t="s">
+      <c r="E4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I4" s="16">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>1898</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>450</v>
       </c>
-      <c r="I15" t="s">
-        <v>265</v>
-      </c>
-      <c r="J15" t="s">
-        <v>0</v>
-      </c>
-      <c r="K15" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="16" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F16">
-        <v>1877</v>
-      </c>
-      <c r="G16" t="s">
-        <v>288</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="I16" t="s">
-        <v>265</v>
-      </c>
-      <c r="J16" t="s">
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="17" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F17">
-        <v>1878</v>
-      </c>
-      <c r="G17" t="s">
-        <v>293</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="I17" t="s">
-        <v>0</v>
-      </c>
-      <c r="J17" t="s">
-        <v>0</v>
-      </c>
-      <c r="K17" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="18" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F18">
-        <v>1878</v>
-      </c>
-      <c r="G18" t="s">
-        <v>288</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>449</v>
-      </c>
-      <c r="I18" t="s">
-        <v>265</v>
-      </c>
-      <c r="J18" t="s">
-        <v>0</v>
-      </c>
-      <c r="K18" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="19" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F19">
-        <v>1879</v>
-      </c>
-      <c r="G19" t="s">
-        <v>288</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="I19" t="s">
-        <v>265</v>
-      </c>
-      <c r="J19" t="s">
-        <v>0</v>
-      </c>
-      <c r="K19" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="20" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F20">
-        <v>1880</v>
-      </c>
-      <c r="G20" t="s">
-        <v>288</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="I20" t="s">
-        <v>265</v>
-      </c>
-      <c r="J20" t="s">
-        <v>0</v>
-      </c>
-      <c r="K20" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="21" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F21">
-        <v>1881</v>
-      </c>
-      <c r="G21" t="s">
-        <v>288</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="I21" t="s">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>0</v>
-      </c>
-      <c r="K21" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="22" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F22">
-        <v>1882</v>
-      </c>
-      <c r="G22" t="s">
-        <v>288</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="I22" t="s">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>0</v>
-      </c>
-      <c r="K22" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="23" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F23">
-        <v>1883</v>
-      </c>
-      <c r="G23" t="s">
-        <v>273</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="I23" t="s">
-        <v>0</v>
-      </c>
-      <c r="J23" t="s">
-        <v>0</v>
-      </c>
-      <c r="K23" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="24" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F24">
-        <v>1883</v>
-      </c>
-      <c r="G24" t="s">
-        <v>286</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="I24" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" t="s">
-        <v>0</v>
-      </c>
-      <c r="K24" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="25" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F25">
-        <v>1884</v>
-      </c>
-      <c r="G25" t="s">
-        <v>273</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="I25" t="s">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>0</v>
-      </c>
-      <c r="K25" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="26" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F26">
-        <v>1885</v>
-      </c>
-      <c r="G26" t="s">
-        <v>273</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>442</v>
-      </c>
-      <c r="I26" t="s">
-        <v>0</v>
-      </c>
-      <c r="J26" t="s">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="27" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F27">
-        <v>1886</v>
-      </c>
-      <c r="G27" t="s">
-        <v>273</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>441</v>
-      </c>
-      <c r="I27" t="s">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
-        <v>0</v>
-      </c>
-      <c r="K27" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="28" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F28">
-        <v>1887</v>
-      </c>
-      <c r="G28" t="s">
-        <v>273</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>440</v>
-      </c>
-      <c r="I28" t="s">
-        <v>0</v>
-      </c>
-      <c r="J28" t="s">
-        <v>0</v>
-      </c>
-      <c r="K28" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="29" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F29">
-        <v>1888</v>
-      </c>
-      <c r="G29" t="s">
-        <v>273</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="I29" t="s">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="30" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F30">
-        <v>1889</v>
-      </c>
-      <c r="G30" t="s">
-        <v>273</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="I30" t="s">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="31" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F31">
-        <v>1890</v>
-      </c>
-      <c r="G31" t="s">
-        <v>273</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="I31" t="s">
-        <v>0</v>
-      </c>
-      <c r="J31" t="s">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="32" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F32">
-        <v>1891</v>
-      </c>
-      <c r="G32" t="s">
-        <v>273</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="I32" t="s">
-        <v>0</v>
-      </c>
-      <c r="J32" t="s">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="33" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F33">
-        <v>1893</v>
-      </c>
-      <c r="G33" t="s">
-        <v>273</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>436</v>
-      </c>
-      <c r="I33" t="s">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
-        <v>265</v>
-      </c>
-      <c r="K33" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="34" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F34">
-        <v>1901</v>
-      </c>
-      <c r="G34" t="s">
-        <v>269</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="I34" t="s">
-        <v>0</v>
-      </c>
-      <c r="J34" t="s">
-        <v>265</v>
-      </c>
-      <c r="K34" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="35" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F35">
-        <v>1901</v>
-      </c>
-      <c r="G35" t="s">
-        <v>270</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="I35" t="s">
-        <v>0</v>
-      </c>
-      <c r="J35" t="s">
-        <v>0</v>
-      </c>
-      <c r="K35" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="36" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F36">
-        <v>1902</v>
-      </c>
-      <c r="G36" t="s">
-        <v>269</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="I36" t="s">
-        <v>0</v>
-      </c>
-      <c r="J36" t="s">
-        <v>265</v>
-      </c>
-      <c r="K36" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="37" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F37">
-        <v>1903</v>
-      </c>
-      <c r="G37" t="s">
-        <v>269</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="I37" t="s">
-        <v>0</v>
-      </c>
-      <c r="J37" t="s">
-        <v>265</v>
-      </c>
-      <c r="K37" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="38" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F38">
-        <v>1904</v>
-      </c>
-      <c r="G38" t="s">
-        <v>269</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="I38" t="s">
-        <v>0</v>
-      </c>
-      <c r="J38" t="s">
-        <v>265</v>
-      </c>
-      <c r="K38" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="39" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F39">
-        <v>1905</v>
-      </c>
-      <c r="G39" t="s">
-        <v>269</v>
-      </c>
-      <c r="H39" s="14" t="s">
-        <v>431</v>
-      </c>
-      <c r="I39" t="s">
-        <v>0</v>
-      </c>
-      <c r="J39" t="s">
-        <v>265</v>
-      </c>
-      <c r="K39" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="40" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F40">
-        <v>1906</v>
-      </c>
-      <c r="G40" t="s">
-        <v>275</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="I40" t="s">
-        <v>0</v>
-      </c>
-      <c r="J40" t="s">
-        <v>265</v>
-      </c>
-      <c r="K40" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="41" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F41">
-        <v>1907</v>
-      </c>
-      <c r="G41" t="s">
-        <v>275</v>
-      </c>
-      <c r="H41" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="I41" t="s">
-        <v>0</v>
-      </c>
-      <c r="J41" t="s">
-        <v>265</v>
-      </c>
-      <c r="K41" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="42" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F42">
-        <v>1908</v>
-      </c>
-      <c r="G42" t="s">
-        <v>275</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="I42" t="s">
-        <v>0</v>
-      </c>
-      <c r="J42" t="s">
-        <v>265</v>
-      </c>
-      <c r="K42" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="43" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F43">
-        <v>1909</v>
-      </c>
-      <c r="G43" t="s">
-        <v>275</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="I43" t="s">
-        <v>0</v>
-      </c>
-      <c r="J43" t="s">
-        <v>265</v>
-      </c>
-      <c r="K43" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="44" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F44">
-        <v>1910</v>
-      </c>
-      <c r="G44" t="s">
-        <v>275</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>431</v>
-      </c>
-      <c r="I44" t="s">
-        <v>0</v>
-      </c>
-      <c r="J44" t="s">
-        <v>265</v>
-      </c>
-      <c r="K44" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="45" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F45">
-        <v>1911</v>
-      </c>
-      <c r="G45" t="s">
-        <v>275</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="I45" t="s">
-        <v>0</v>
-      </c>
-      <c r="J45" t="s">
-        <v>265</v>
-      </c>
-      <c r="K45" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="46" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F46">
-        <v>1912</v>
-      </c>
-      <c r="G46" t="s">
-        <v>335</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="I46" t="s">
-        <v>0</v>
-      </c>
-      <c r="J46" t="s">
-        <v>0</v>
-      </c>
-      <c r="K46" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="47" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F47">
-        <v>1912</v>
-      </c>
-      <c r="G47" t="s">
-        <v>275</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="I47" t="s">
-        <v>0</v>
-      </c>
-      <c r="J47" t="s">
-        <v>265</v>
-      </c>
-      <c r="K47" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="48" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F48">
-        <v>1913</v>
-      </c>
-      <c r="G48" t="s">
-        <v>335</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="I48" t="s">
-        <v>0</v>
-      </c>
-      <c r="J48" t="s">
-        <v>265</v>
-      </c>
-      <c r="K48" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="49" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F49">
-        <v>1913</v>
-      </c>
-      <c r="G49" t="s">
-        <v>275</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>430</v>
-      </c>
-      <c r="I49" t="s">
-        <v>0</v>
-      </c>
-      <c r="J49" t="s">
-        <v>0</v>
-      </c>
-      <c r="K49" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="50" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F50">
-        <v>1914</v>
-      </c>
-      <c r="G50" t="s">
-        <v>335</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="I50" t="s">
-        <v>0</v>
-      </c>
-      <c r="J50" t="s">
-        <v>265</v>
-      </c>
-      <c r="K50" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="51" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F51">
-        <v>1915</v>
-      </c>
-      <c r="G51" t="s">
-        <v>262</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="I51" t="s">
-        <v>0</v>
-      </c>
-      <c r="J51" t="s">
-        <v>265</v>
-      </c>
-      <c r="K51" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="52" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F52">
-        <v>1916</v>
-      </c>
-      <c r="G52" t="s">
-        <v>262</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="I52" t="s">
-        <v>0</v>
-      </c>
-      <c r="J52" t="s">
-        <v>265</v>
-      </c>
-      <c r="K52" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="53" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F53">
-        <v>1917</v>
-      </c>
-      <c r="G53" t="s">
-        <v>262</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="I53" t="s">
-        <v>0</v>
-      </c>
-      <c r="J53" t="s">
-        <v>265</v>
-      </c>
-      <c r="K53" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="54" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H54" s="14"/>
-    </row>
-    <row r="55" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H55" s="14"/>
-    </row>
-    <row r="56" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H56" s="14"/>
-    </row>
-    <row r="57" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H57" s="14"/>
-    </row>
-    <row r="58" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H58" s="14"/>
-    </row>
-    <row r="59" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H59" s="14"/>
-    </row>
-    <row r="60" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H60" s="14"/>
-    </row>
-    <row r="61" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H61" s="14"/>
-    </row>
-    <row r="62" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H62" s="14"/>
-    </row>
-    <row r="63" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H63" s="14"/>
-    </row>
-    <row r="64" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="H64" s="14"/>
-    </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H65" s="14"/>
-    </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H66" s="14"/>
-    </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H67" s="14"/>
-    </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H68" s="14"/>
-    </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H69" s="14"/>
-    </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H70" s="14"/>
-    </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H71" s="14"/>
-    </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H72" s="14"/>
-    </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H73" s="14"/>
-    </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H74" s="14"/>
-    </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H75" s="14"/>
-    </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H76" s="14"/>
-    </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H77" s="14"/>
-    </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H78" s="14"/>
-    </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H79" s="14"/>
-    </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H80" s="14"/>
-    </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H81" s="14"/>
-    </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H82" s="14"/>
-    </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H83" s="14"/>
-    </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H84" s="14"/>
-    </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H85" s="14"/>
-    </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.35">
-      <c r="H86" s="14"/>
+      <c r="E5" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="16">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="F4:K4" xr:uid="{7E02B6B0-E213-4BD1-B779-1B5FAA895902}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F5:K53">
-      <sortCondition ref="F4"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="B2:G2" xr:uid="{02AF99F0-2951-4CDD-B3E0-7A8779F916A1}"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="containsText" dxfId="21" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -8223,26 +7712,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="26"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="31" t="s">
+      <c r="D1" s="33"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="37" t="s">
+      <c r="G1" s="37"/>
+      <c r="H1" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="38"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -9935,7 +9424,7 @@
     <mergeCell ref="H1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="H3 H20:I28 H30:I31 H13:I18">
-    <cfRule type="containsText" dxfId="195" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="217" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9952,7 +9441,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:I7">
-    <cfRule type="containsText" dxfId="194" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="216" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9969,7 +9458,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:I48 H50:I50 H52:I52">
-    <cfRule type="containsText" dxfId="193" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="215" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H48))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9986,7 +9475,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:I34">
-    <cfRule type="containsText" dxfId="192" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="214" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10003,7 +9492,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35">
-    <cfRule type="containsText" dxfId="191" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="213" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10020,7 +9509,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:I4">
-    <cfRule type="containsText" dxfId="190" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="212" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10037,7 +9526,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="189" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="211" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10054,7 +9543,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:I12">
-    <cfRule type="containsText" dxfId="188" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="210" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10071,7 +9560,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39:I39">
-    <cfRule type="containsText" dxfId="187" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="209" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10088,7 +9577,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H12">
-    <cfRule type="containsText" dxfId="186" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="208" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10105,7 +9594,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H49:I49 H51:I51 H53:I53">
-    <cfRule type="containsText" dxfId="185" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="207" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10122,7 +9611,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="184" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="206" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10139,7 +9628,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H55:I55">
-    <cfRule type="containsText" dxfId="183" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="205" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10156,7 +9645,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:I19">
-    <cfRule type="containsText" dxfId="182" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="204" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10173,7 +9662,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:I33">
-    <cfRule type="containsText" dxfId="181" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="203" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10190,7 +9679,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H36:I36">
-    <cfRule type="containsText" dxfId="180" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="202" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10207,7 +9696,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37:I37">
-    <cfRule type="containsText" dxfId="179" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="201" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10224,7 +9713,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38:I38">
-    <cfRule type="containsText" dxfId="178" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="200" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10241,7 +9730,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H54:I54">
-    <cfRule type="containsText" dxfId="177" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="199" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10258,7 +9747,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:I32">
-    <cfRule type="containsText" dxfId="176" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="198" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10275,7 +9764,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H47:I47">
-    <cfRule type="containsText" dxfId="175" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="197" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10313,25 +9802,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="26"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="31" t="s">
+      <c r="D1" s="34"/>
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37" t="s">
+      <c r="F1" s="37"/>
+      <c r="G1" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="38"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -11821,7 +11310,7 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3 G20:H28 G30:H31 G13:H18">
-    <cfRule type="containsText" dxfId="174" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="196" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11838,7 +11327,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:H7">
-    <cfRule type="containsText" dxfId="173" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="195" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11855,7 +11344,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G48:H48 G50:H50 G52:H52">
-    <cfRule type="containsText" dxfId="172" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="194" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G48))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11872,7 +11361,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34:H34">
-    <cfRule type="containsText" dxfId="171" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="193" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11889,7 +11378,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:H35">
-    <cfRule type="containsText" dxfId="170" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="192" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11906,7 +11395,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H4">
-    <cfRule type="containsText" dxfId="169" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="191" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11923,7 +11412,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="168" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="190" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11940,7 +11429,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H12">
-    <cfRule type="containsText" dxfId="167" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="189" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11957,7 +11446,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G39:H39">
-    <cfRule type="containsText" dxfId="166" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="188" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11974,7 +11463,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G12">
-    <cfRule type="containsText" dxfId="165" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="187" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11991,7 +11480,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G49:H49 G51:H51 G53:H53">
-    <cfRule type="containsText" dxfId="164" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="186" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12008,7 +11497,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="163" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="185" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12025,7 +11514,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:H19">
-    <cfRule type="containsText" dxfId="162" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="184" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12042,7 +11531,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33:H33">
-    <cfRule type="containsText" dxfId="161" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="183" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12059,7 +11548,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36:H36">
-    <cfRule type="containsText" dxfId="160" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="182" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12076,7 +11565,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G37:H37">
-    <cfRule type="containsText" dxfId="159" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="181" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12093,7 +11582,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:H38">
-    <cfRule type="containsText" dxfId="158" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="180" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12110,7 +11599,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G54:H54">
-    <cfRule type="containsText" dxfId="157" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="179" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12127,7 +11616,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:H32">
-    <cfRule type="containsText" dxfId="156" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="178" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12144,7 +11633,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G47:H47">
-    <cfRule type="containsText" dxfId="155" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="177" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12161,7 +11650,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29:H29">
-    <cfRule type="containsText" dxfId="154" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="176" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12178,7 +11667,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41:H41 G43:H43 G45:H45">
-    <cfRule type="containsText" dxfId="153" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="175" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G41))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12195,7 +11684,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 G42:H42 G44:H44 G46:H46">
-    <cfRule type="containsText" dxfId="152" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="174" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12233,25 +11722,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="26"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="31" t="s">
+      <c r="D1" s="34"/>
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37" t="s">
+      <c r="F1" s="37"/>
+      <c r="G1" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="38"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -13741,7 +13230,7 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3 G20:H28 G13:H18 G30:H31 H33:H34 H36:H37">
-    <cfRule type="containsText" dxfId="151" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="173" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13758,7 +13247,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:H7">
-    <cfRule type="containsText" dxfId="150" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="172" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13775,7 +13264,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G48:H48 G50:H50 G52:H52">
-    <cfRule type="containsText" dxfId="149" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="171" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G48))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13792,7 +13281,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="containsText" dxfId="148" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="170" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13809,7 +13298,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35">
-    <cfRule type="containsText" dxfId="147" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="169" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13826,7 +13315,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H4">
-    <cfRule type="containsText" dxfId="146" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="168" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13843,7 +13332,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="145" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="167" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13860,7 +13349,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H12">
-    <cfRule type="containsText" dxfId="144" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="166" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13877,7 +13366,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G39:H39">
-    <cfRule type="containsText" dxfId="143" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="165" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13894,7 +13383,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G12">
-    <cfRule type="containsText" dxfId="142" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="164" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13911,7 +13400,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G49:H49 G51:H51 G53:H53">
-    <cfRule type="containsText" dxfId="141" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="163" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13928,7 +13417,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="140" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="162" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13945,7 +13434,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:H19">
-    <cfRule type="containsText" dxfId="139" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="161" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13962,7 +13451,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33">
-    <cfRule type="containsText" dxfId="138" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="160" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13979,7 +13468,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36">
-    <cfRule type="containsText" dxfId="137" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="159" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13996,7 +13485,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G37">
-    <cfRule type="containsText" dxfId="136" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="158" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14013,7 +13502,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38">
-    <cfRule type="containsText" dxfId="135" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="157" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14030,7 +13519,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G54:H54">
-    <cfRule type="containsText" dxfId="134" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="156" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14047,7 +13536,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32">
-    <cfRule type="containsText" dxfId="133" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="155" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14064,7 +13553,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G47:H47">
-    <cfRule type="containsText" dxfId="132" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="154" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14081,7 +13570,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29:H29 H32 H35 H38">
-    <cfRule type="containsText" dxfId="131" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="153" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14098,7 +13587,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41:H41 G43:H43 G45:H45">
-    <cfRule type="containsText" dxfId="130" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="152" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G41))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14115,7 +13604,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 G42:H42 G44:H44 G46:H46">
-    <cfRule type="containsText" dxfId="129" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="151" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14153,25 +13642,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="26"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="31" t="s">
+      <c r="D1" s="34"/>
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37" t="s">
+      <c r="F1" s="37"/>
+      <c r="G1" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="H1" s="38"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -15673,7 +15162,7 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3 G13:H18 G30:H31 H33:H34 H36:H37 G20:H28">
-    <cfRule type="containsText" dxfId="128" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="150" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15690,7 +15179,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:H7">
-    <cfRule type="containsText" dxfId="127" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="149" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15707,7 +15196,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G48:H48 G50:H50 G52:H52">
-    <cfRule type="containsText" dxfId="126" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="148" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G48))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15724,7 +15213,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="containsText" dxfId="125" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="147" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15741,7 +15230,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35">
-    <cfRule type="containsText" dxfId="124" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="146" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15758,7 +15247,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:H4">
-    <cfRule type="containsText" dxfId="123" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="145" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15775,7 +15264,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="122" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="144" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15792,7 +15281,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:H12">
-    <cfRule type="containsText" dxfId="121" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="143" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15809,7 +15298,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G39:H39">
-    <cfRule type="containsText" dxfId="120" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="142" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15826,7 +15315,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G12">
-    <cfRule type="containsText" dxfId="119" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="141" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15843,7 +15332,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G49:H49 G51:H51 G53:H53">
-    <cfRule type="containsText" dxfId="118" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="140" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15860,7 +15349,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="containsText" dxfId="117" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="139" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15877,7 +15366,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:H19">
-    <cfRule type="containsText" dxfId="116" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="138" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15894,7 +15383,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33">
-    <cfRule type="containsText" dxfId="115" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="137" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15911,7 +15400,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36">
-    <cfRule type="containsText" dxfId="114" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="136" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15928,7 +15417,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G37">
-    <cfRule type="containsText" dxfId="113" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="135" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15945,7 +15434,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38">
-    <cfRule type="containsText" dxfId="112" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="134" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15962,7 +15451,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G54:H54">
-    <cfRule type="containsText" dxfId="111" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="133" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15979,7 +15468,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32">
-    <cfRule type="containsText" dxfId="110" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="132" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15996,7 +15485,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G47:H47">
-    <cfRule type="containsText" dxfId="109" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="131" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16013,7 +15502,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29:H29 H32 H35 H38">
-    <cfRule type="containsText" dxfId="108" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="130" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16030,7 +15519,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41:H41 G43:H43 G45:H45">
-    <cfRule type="containsText" dxfId="107" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="129" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G41))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16047,7 +15536,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40 G42:H42 G44:H44 G46:H46">
-    <cfRule type="containsText" dxfId="106" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="128" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16085,25 +15574,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="27"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="31" t="s">
+      <c r="D1" s="34"/>
+      <c r="E1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37" t="s">
+      <c r="F1" s="37"/>
+      <c r="G1" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="H1" s="38"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -16171,7 +15660,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>0</v>
@@ -16196,7 +15685,7 @@
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="14" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>5</v>
@@ -16229,7 +15718,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>0</v>
@@ -16254,10 +15743,10 @@
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="14" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G7" s="16">
         <v>0</v>
@@ -16287,7 +15776,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>0</v>
@@ -16312,10 +15801,10 @@
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="14" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="G9" s="16">
         <v>0</v>
@@ -16345,7 +15834,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>0</v>
@@ -16370,10 +15859,10 @@
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="14" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="G11" s="16">
         <v>0</v>
@@ -16403,7 +15892,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>0</v>
@@ -16428,7 +15917,7 @@
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="14" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>0</v>
@@ -16461,7 +15950,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>0</v>
@@ -16486,7 +15975,7 @@
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="14" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>0</v>
@@ -16519,7 +16008,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>0</v>
@@ -16544,7 +16033,7 @@
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="14" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>0</v>
@@ -16577,7 +16066,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>0</v>
@@ -16602,7 +16091,7 @@
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="14" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>0</v>
@@ -16635,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>0</v>
@@ -16660,7 +16149,7 @@
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="14" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>0</v>
@@ -16693,7 +16182,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>0</v>
@@ -16718,10 +16207,10 @@
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="14" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G23" s="16">
         <v>0</v>
@@ -16751,7 +16240,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>0</v>
@@ -16775,7 +16264,7 @@
         <v>260</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>0</v>
@@ -16809,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>0</v>
@@ -16863,13 +16352,13 @@
         <v>260</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>0</v>
@@ -16897,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>0</v>
@@ -16921,13 +16410,13 @@
         <v>260</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>0</v>
@@ -16955,7 +16444,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>0</v>
@@ -16979,13 +16468,13 @@
         <v>260</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>0</v>
@@ -17013,7 +16502,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>0</v>
@@ -17037,13 +16526,13 @@
         <v>260</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>0</v>
@@ -17071,7 +16560,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>0</v>
@@ -17095,13 +16584,13 @@
         <v>260</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E36" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>0</v>
@@ -17125,13 +16614,13 @@
         <v>260</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E37" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>0</v>
@@ -17155,7 +16644,7 @@
         <v>260</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E38" s="17" t="s">
         <v>0</v>
@@ -17185,13 +16674,13 @@
         <v>260</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E39" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>0</v>
@@ -17215,13 +16704,13 @@
         <v>260</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E40" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>0</v>
@@ -17245,13 +16734,13 @@
         <v>260</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>0</v>
@@ -17275,13 +16764,13 @@
         <v>260</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E42" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>0</v>
@@ -17305,13 +16794,13 @@
         <v>260</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>0</v>
@@ -17335,13 +16824,13 @@
         <v>260</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E44" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>0</v>
@@ -17365,13 +16854,13 @@
         <v>260</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>0</v>
@@ -17395,13 +16884,13 @@
         <v>260</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>0</v>
@@ -17425,13 +16914,13 @@
         <v>260</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>0</v>
@@ -17455,7 +16944,7 @@
         <v>260</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E48" s="17" t="s">
         <v>0</v>
@@ -17575,13 +17064,13 @@
         <v>260</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E52" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>0</v>
@@ -17605,13 +17094,13 @@
         <v>260</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>0</v>
@@ -17635,13 +17124,13 @@
         <v>260</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E54" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>0</v>
@@ -17665,7 +17154,7 @@
         <v>260</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E55" s="17" t="s">
         <v>0</v>
@@ -17695,13 +17184,13 @@
         <v>260</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E56" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>0</v>
@@ -17725,13 +17214,13 @@
         <v>260</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E57" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>0</v>
@@ -17755,7 +17244,7 @@
         <v>260</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E58" s="17" t="s">
         <v>0</v>
@@ -17785,7 +17274,7 @@
         <v>260</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E59" s="17" t="s">
         <v>0</v>
@@ -17815,7 +17304,7 @@
         <v>260</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E60" s="17" t="s">
         <v>0</v>
@@ -17845,7 +17334,7 @@
         <v>260</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E61" s="17" t="s">
         <v>0</v>
@@ -17875,7 +17364,7 @@
         <v>260</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E62" s="17" t="s">
         <v>0</v>
@@ -17905,7 +17394,7 @@
         <v>260</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E63" s="17" t="s">
         <v>0</v>
@@ -17965,7 +17454,7 @@
         <v>260</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>0</v>
@@ -17995,13 +17484,13 @@
         <v>260</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E66" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>0</v>
@@ -18025,7 +17514,7 @@
         <v>260</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E67" s="17" t="s">
         <v>0</v>
@@ -18055,13 +17544,13 @@
         <v>260</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E68" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>0</v>
@@ -18089,7 +17578,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>0</v>
@@ -18113,13 +17602,13 @@
         <v>260</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E70" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>0</v>
@@ -18147,7 +17636,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>0</v>
@@ -18171,7 +17660,7 @@
         <v>260</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E72" s="17" t="s">
         <v>0</v>
@@ -18201,13 +17690,13 @@
         <v>260</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E73" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>0</v>
@@ -18231,13 +17720,13 @@
         <v>260</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E74" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>0</v>
@@ -18261,7 +17750,7 @@
         <v>260</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E75" s="17" t="s">
         <v>0</v>
@@ -18347,7 +17836,7 @@
     <mergeCell ref="G1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G48:H48 H52 H54:H55 H37 G3:G4 G27:H27 G30:H30 G39:H39 G46:H46 G6 G8 G10 G12 G14 G16 G18 G20 G22 G24 G32:H32 G34:H34 G36:G37">
-    <cfRule type="containsText" dxfId="105" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="127" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18364,7 +17853,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6 H10 H14 H18 H22">
-    <cfRule type="containsText" dxfId="104" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="126" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18381,7 +17870,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G68:H68 G72:H72 G75:H75">
-    <cfRule type="containsText" dxfId="103" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="125" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G68))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18398,7 +17887,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G52">
-    <cfRule type="containsText" dxfId="102" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="124" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G52))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18415,7 +17904,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G53">
-    <cfRule type="containsText" dxfId="101" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="123" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G53))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18432,7 +17921,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8 H12 H16 H20 H24 H4:H5">
-    <cfRule type="containsText" dxfId="100" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="122" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18449,7 +17938,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="containsText" dxfId="99" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="121" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18466,7 +17955,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G54">
-    <cfRule type="containsText" dxfId="98" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="120" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18483,7 +17972,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59:H59">
-    <cfRule type="containsText" dxfId="97" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="119" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G59))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18500,7 +17989,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G70:H70 G74:H74">
-    <cfRule type="containsText" dxfId="96" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="118" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G70))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18517,7 +18006,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G61:H61 G63:H63 G65:H65">
-    <cfRule type="containsText" dxfId="95" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="117" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G61))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18534,7 +18023,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H36">
-    <cfRule type="containsText" dxfId="94" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="116" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18551,7 +18040,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G67:H67">
-    <cfRule type="containsText" dxfId="93" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="115" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G67))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18568,7 +18057,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G47:H47 H53 H57">
-    <cfRule type="containsText" dxfId="92" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="114" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18585,7 +18074,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G60:H60 G62:H62 G66:H66">
-    <cfRule type="containsText" dxfId="91" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="113" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G60))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18602,7 +18091,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G55">
-    <cfRule type="containsText" dxfId="90" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="112" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18619,7 +18108,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57">
-    <cfRule type="containsText" dxfId="89" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="111" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G57))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18636,7 +18125,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="containsText" dxfId="88" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="110" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18653,7 +18142,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="containsText" dxfId="87" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="109" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18670,7 +18159,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40:H40">
-    <cfRule type="containsText" dxfId="86" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="108" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18687,7 +18176,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="85" priority="135" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="107" priority="135" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18704,7 +18193,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41:H41">
-    <cfRule type="containsText" dxfId="84" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="106" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G41))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18721,7 +18210,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:H38">
-    <cfRule type="containsText" dxfId="83" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="105" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18738,7 +18227,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="containsText" dxfId="82" priority="133" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="104" priority="133" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18755,7 +18244,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:H43">
-    <cfRule type="containsText" dxfId="81" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="103" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G43))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18772,7 +18261,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42:H42">
-    <cfRule type="containsText" dxfId="80" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="102" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G42))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18789,7 +18278,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G44:H44">
-    <cfRule type="containsText" dxfId="79" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="101" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G44))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18806,7 +18295,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G45:H45">
-    <cfRule type="containsText" dxfId="78" priority="121" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="100" priority="121" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G45))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18823,7 +18312,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G49:H51">
-    <cfRule type="containsText" dxfId="77" priority="117" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="99" priority="117" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18840,7 +18329,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G58">
-    <cfRule type="containsText" dxfId="76" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="98" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G58))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18857,7 +18346,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58">
-    <cfRule type="containsText" dxfId="75" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="97" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H58))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18874,7 +18363,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="containsText" dxfId="74" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="96" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G56))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18891,7 +18380,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H56">
-    <cfRule type="containsText" dxfId="73" priority="109" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="95" priority="109" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H56))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18908,7 +18397,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64:H64">
-    <cfRule type="containsText" dxfId="72" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="94" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G64))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18925,7 +18414,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="containsText" dxfId="71" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="93" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18942,7 +18431,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="70" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="92" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18959,7 +18448,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G73:H73">
-    <cfRule type="containsText" dxfId="69" priority="105" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="91" priority="105" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G73))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18976,7 +18465,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="68" priority="99" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="90" priority="99" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18993,7 +18482,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9">
-    <cfRule type="containsText" dxfId="67" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="89" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19010,7 +18499,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="containsText" dxfId="66" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="88" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19027,7 +18516,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
-    <cfRule type="containsText" dxfId="65" priority="87" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="87" priority="87" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19044,7 +18533,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9">
-    <cfRule type="containsText" dxfId="64" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="86" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G9))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19061,7 +18550,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23">
-    <cfRule type="containsText" dxfId="63" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="85" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19078,7 +18567,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23">
-    <cfRule type="containsText" dxfId="62" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="84" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19095,7 +18584,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26">
-    <cfRule type="containsText" dxfId="61" priority="57" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="83" priority="57" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19112,7 +18601,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="containsText" dxfId="60" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="82" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19129,7 +18618,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="59" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="81" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19146,7 +18635,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15">
-    <cfRule type="containsText" dxfId="58" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="80" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19163,7 +18652,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="57" priority="49" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="79" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19180,7 +18669,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21">
-    <cfRule type="containsText" dxfId="56" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G21))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19197,7 +18686,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="55" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19214,7 +18703,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17">
-    <cfRule type="containsText" dxfId="54" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G17))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19231,7 +18720,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19">
-    <cfRule type="containsText" dxfId="53" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19248,7 +18737,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="containsText" dxfId="52" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19265,12 +18754,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="51" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="50" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19299,7 +18788,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19">
-    <cfRule type="containsText" dxfId="49" priority="37" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="37" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19316,7 +18805,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21">
-    <cfRule type="containsText" dxfId="48" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H21))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19333,7 +18822,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="containsText" dxfId="47" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H29))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19350,7 +18839,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G31">
-    <cfRule type="containsText" dxfId="46" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19367,12 +18856,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G33">
-    <cfRule type="containsText" dxfId="45" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="containsText" dxfId="44" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19401,12 +18890,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35">
-    <cfRule type="containsText" dxfId="43" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35">
-    <cfRule type="containsText" dxfId="42" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H35))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19435,12 +18924,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69">
-    <cfRule type="containsText" dxfId="41" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G69))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H69">
-    <cfRule type="containsText" dxfId="40" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H69))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19469,12 +18958,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G71">
-    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G71))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H71">
-    <cfRule type="containsText" dxfId="38" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H71))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19503,12 +18992,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G76">
-    <cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G76))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H76">
-    <cfRule type="containsText" dxfId="36" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H76))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19537,12 +19026,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G77">
-    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G77))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H77">
-    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H77))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19592,24 +19081,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="27"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33"/>
+      <c r="D1" s="34"/>
       <c r="E1" s="27" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="G1"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -19641,7 +19130,7 @@
         <v>261</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="F3" s="16">
         <v>0</v>
@@ -19665,7 +19154,7 @@
         <v>261</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="F4" s="16">
         <v>0</v>
@@ -19689,7 +19178,7 @@
         <v>261</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="F5" s="16">
         <v>0</v>
@@ -19713,7 +19202,7 @@
         <v>261</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="F6" s="16">
         <v>0</v>
@@ -19737,7 +19226,7 @@
         <v>261</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="F7" s="16">
         <v>0</v>
@@ -19761,7 +19250,7 @@
         <v>261</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="F8" s="16">
         <v>0</v>
@@ -19785,7 +19274,7 @@
         <v>261</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="F9" s="16">
         <v>0</v>
@@ -19809,7 +19298,7 @@
         <v>261</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="F10" s="16">
         <v>0</v>
@@ -19833,7 +19322,7 @@
         <v>261</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="F11" s="16">
         <v>0</v>
@@ -19857,7 +19346,7 @@
         <v>261</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="F12" s="16">
         <v>0</v>
@@ -19881,7 +19370,7 @@
         <v>261</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="F13" s="16">
         <v>0</v>
@@ -19902,7 +19391,7 @@
         <v>260</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>5</v>
@@ -19950,10 +19439,10 @@
         <v>260</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="F16" s="16">
         <v>0</v>
@@ -19974,10 +19463,10 @@
         <v>260</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="F17" s="16">
         <v>0</v>
@@ -19998,10 +19487,10 @@
         <v>260</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="F18" s="16">
         <v>0</v>
@@ -20022,10 +19511,10 @@
         <v>260</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="F19" s="16">
         <v>0</v>
@@ -20046,10 +19535,10 @@
         <v>260</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="F20" s="16">
         <v>0</v>
@@ -20070,10 +19559,10 @@
         <v>260</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="F21" s="16">
         <v>0</v>
@@ -20094,7 +19583,7 @@
         <v>260</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>5</v>
@@ -20118,10 +19607,10 @@
         <v>260</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="F23" s="16">
         <v>0</v>
@@ -20142,10 +19631,10 @@
         <v>260</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="F24" s="16">
         <v>0</v>
@@ -20166,10 +19655,10 @@
         <v>260</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F25" s="16">
         <v>0</v>
@@ -20190,10 +19679,10 @@
         <v>260</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="F26" s="16">
         <v>0</v>
@@ -20214,7 +19703,7 @@
         <v>260</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>52</v>
@@ -20238,10 +19727,10 @@
         <v>260</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="F28" s="16">
         <v>0</v>
@@ -20262,10 +19751,10 @@
         <v>260</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="F29" s="16">
         <v>0</v>
@@ -20286,10 +19775,10 @@
         <v>260</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="F30" s="16">
         <v>0</v>
@@ -20334,10 +19823,10 @@
         <v>260</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="F32" s="16">
         <v>0</v>
@@ -20358,7 +19847,7 @@
         <v>260</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>52</v>
@@ -20382,7 +19871,7 @@
         <v>260</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>44</v>
@@ -20406,10 +19895,10 @@
         <v>260</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="F35" s="16">
         <v>0</v>
@@ -20430,7 +19919,7 @@
         <v>260</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>53</v>
@@ -20454,10 +19943,10 @@
         <v>260</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="F37" s="16">
         <v>0</v>
@@ -20478,10 +19967,10 @@
         <v>260</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="F38" s="16">
         <v>0</v>
@@ -20502,7 +19991,7 @@
         <v>260</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>5</v>
@@ -20526,10 +20015,10 @@
         <v>260</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="F40" s="16">
         <v>0</v>
@@ -20550,7 +20039,7 @@
         <v>260</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>169</v>
@@ -20574,7 +20063,7 @@
         <v>260</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>5</v>
@@ -20598,10 +20087,10 @@
         <v>260</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="F43" s="16">
         <v>0</v>
@@ -20622,10 +20111,10 @@
         <v>260</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="F44" s="16">
         <v>0</v>
@@ -20646,7 +20135,7 @@
         <v>260</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>118</v>
@@ -20670,10 +20159,10 @@
         <v>260</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="F46" s="16">
         <v>1</v>
@@ -20694,7 +20183,7 @@
         <v>260</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>174</v>
@@ -20718,7 +20207,7 @@
         <v>260</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>118</v>
@@ -20742,10 +20231,10 @@
         <v>260</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="F49" s="16">
         <v>0</v>
@@ -20766,10 +20255,10 @@
         <v>260</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="F50" s="16">
         <v>0</v>
@@ -20790,7 +20279,7 @@
         <v>260</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>118</v>
@@ -20814,10 +20303,10 @@
         <v>260</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="F52" s="16">
         <v>0</v>
@@ -20838,7 +20327,7 @@
         <v>260</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>118</v>
@@ -20862,7 +20351,7 @@
         <v>260</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E54" s="30" t="s">
         <v>5</v>
@@ -20886,10 +20375,10 @@
         <v>260</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="F55" s="16">
         <v>0</v>
@@ -20910,10 +20399,10 @@
         <v>260</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="F56" s="16">
         <v>0</v>
@@ -20934,10 +20423,10 @@
         <v>260</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="F57" s="16">
         <v>0</v>
@@ -20958,10 +20447,10 @@
         <v>260</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="F58" s="16">
         <v>0</v>
@@ -20982,10 +20471,10 @@
         <v>260</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="F59" s="16">
         <v>0</v>
@@ -21006,7 +20495,7 @@
         <v>260</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>108</v>
@@ -21026,7 +20515,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F35:F36 F38 F43:F53 F3:F13 F15 F17:F30 F32:F33 F40 F55:F58 F60">
-    <cfRule type="containsText" dxfId="33" priority="59" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="59" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21043,7 +20532,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34 F37 F41">
-    <cfRule type="containsText" dxfId="32" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21060,7 +20549,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="31" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21077,7 +20566,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21094,7 +20583,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21111,7 +20600,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21128,7 +20617,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42">
-    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F42))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21145,7 +20634,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="containsText" dxfId="26" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21162,7 +20651,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F59))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21200,24 +20689,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="27"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33"/>
+      <c r="D1" s="34"/>
       <c r="E1" s="27" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="G1"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -21249,7 +20738,7 @@
         <v>261</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="F3" s="16">
         <v>0</v>
@@ -21273,7 +20762,7 @@
         <v>261</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="F4" s="16">
         <v>0</v>
@@ -21297,7 +20786,7 @@
         <v>261</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="F5" s="16">
         <v>0</v>
@@ -21321,7 +20810,7 @@
         <v>261</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="F6" s="16">
         <v>0</v>
@@ -21345,7 +20834,7 @@
         <v>261</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="F7" s="16">
         <v>0</v>
@@ -21369,7 +20858,7 @@
         <v>261</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="F8" s="16">
         <v>0</v>
@@ -21393,7 +20882,7 @@
         <v>261</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="F9" s="16">
         <v>0</v>
@@ -21417,7 +20906,7 @@
         <v>261</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F10" s="16">
         <v>0</v>
@@ -21441,7 +20930,7 @@
         <v>261</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="F11" s="16">
         <v>0</v>
@@ -21465,7 +20954,7 @@
         <v>261</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="F12" s="16">
         <v>0</v>
@@ -21489,7 +20978,7 @@
         <v>261</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="F13" s="16">
         <v>0</v>
@@ -21510,7 +20999,7 @@
         <v>260</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>5</v>
@@ -21534,10 +21023,10 @@
         <v>260</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="F15" s="16">
         <v>0</v>
@@ -21558,10 +21047,10 @@
         <v>260</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="F16" s="16">
         <v>0</v>
@@ -21582,10 +21071,10 @@
         <v>260</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="F17" s="16">
         <v>0</v>
@@ -21606,10 +21095,10 @@
         <v>260</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="F18" s="16">
         <v>0</v>
@@ -21630,10 +21119,10 @@
         <v>260</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="F19" s="16">
         <v>0</v>
@@ -21654,7 +21143,7 @@
         <v>260</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>5</v>
@@ -21678,10 +21167,10 @@
         <v>260</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="F21" s="16">
         <v>0</v>
@@ -21702,7 +21191,7 @@
         <v>260</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>5</v>
@@ -21726,10 +21215,10 @@
         <v>260</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="F23" s="16">
         <v>0</v>
@@ -21750,10 +21239,10 @@
         <v>260</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="F24" s="16">
         <v>0</v>
@@ -21774,10 +21263,10 @@
         <v>260</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="F25" s="16">
         <v>0</v>
@@ -21798,10 +21287,10 @@
         <v>260</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F26" s="16">
         <v>0</v>
@@ -21822,7 +21311,7 @@
         <v>260</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>5</v>
@@ -21846,10 +21335,10 @@
         <v>260</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="F28" s="16">
         <v>0</v>
@@ -21870,10 +21359,10 @@
         <v>260</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="F29" s="16">
         <v>0</v>
@@ -21894,10 +21383,10 @@
         <v>260</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="F30" s="16">
         <v>0</v>
@@ -21942,10 +21431,10 @@
         <v>260</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="F32" s="16">
         <v>0</v>
@@ -22014,10 +21503,10 @@
         <v>260</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="F35" s="16">
         <v>0</v>
@@ -22038,10 +21527,10 @@
         <v>260</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="F36" s="16">
         <v>0</v>
@@ -22062,10 +21551,10 @@
         <v>260</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="F37" s="16">
         <v>0</v>
@@ -22086,10 +21575,10 @@
         <v>260</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="F38" s="16">
         <v>0</v>
@@ -22110,7 +21599,7 @@
         <v>260</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>5</v>
@@ -22134,10 +21623,10 @@
         <v>260</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="F40" s="16">
         <v>0</v>
@@ -22158,10 +21647,10 @@
         <v>260</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="F41" s="16">
         <v>0</v>
@@ -22182,7 +21671,7 @@
         <v>260</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>5</v>
@@ -22206,10 +21695,10 @@
         <v>260</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="F43" s="16">
         <v>0</v>
@@ -22230,10 +21719,10 @@
         <v>260</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="F44" s="16">
         <v>0</v>
@@ -22254,10 +21743,10 @@
         <v>260</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="F45" s="16">
         <v>0</v>
@@ -22278,7 +21767,7 @@
         <v>260</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E46" s="14" t="s">
         <v>96</v>
@@ -22302,10 +21791,10 @@
         <v>260</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="F47" s="16">
         <v>0</v>
@@ -22326,7 +21815,7 @@
         <v>260</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>122</v>
@@ -22350,10 +21839,10 @@
         <v>260</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="F49" s="16">
         <v>0</v>
@@ -22374,10 +21863,10 @@
         <v>260</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="F50" s="16">
         <v>0</v>
@@ -22422,10 +21911,10 @@
         <v>260</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="F52" s="16">
         <v>0</v>
@@ -22446,10 +21935,10 @@
         <v>260</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="F53" s="16">
         <v>0</v>
@@ -22470,7 +21959,7 @@
         <v>260</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>5</v>
@@ -22494,7 +21983,7 @@
         <v>260</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E55" s="30" t="s">
         <v>5</v>
@@ -22518,10 +22007,10 @@
         <v>260</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="F56" s="16">
         <v>0</v>
@@ -22542,10 +22031,10 @@
         <v>260</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="F57" s="16">
         <v>0</v>
@@ -22566,10 +22055,10 @@
         <v>260</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="F58" s="16">
         <v>1</v>
@@ -22590,10 +22079,10 @@
         <v>260</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="F59" s="16">
         <v>0</v>
@@ -22614,10 +22103,10 @@
         <v>260</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="F60" s="16">
         <v>0</v>
@@ -22638,10 +22127,10 @@
         <v>260</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F61" s="16">
         <v>0</v>
@@ -22658,7 +22147,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F35:F36 F38 F3:F13 F16:F19 F32 F40 F56:F59 F61 F43:F50 F21:F30 F52:F54">
-    <cfRule type="containsText" dxfId="24" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22675,7 +22164,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37 F41">
-    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F37))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22692,7 +22181,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="22" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22709,7 +22198,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="21" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22726,7 +22215,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="20" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22743,7 +22232,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F39))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22760,7 +22249,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42">
-    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F42))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22777,7 +22266,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="containsText" dxfId="17" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22794,7 +22283,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60">
-    <cfRule type="containsText" dxfId="16" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F60))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22811,7 +22300,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22828,7 +22317,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22845,7 +22334,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22862,7 +22351,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F51))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22900,24 +22389,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="27"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33"/>
+      <c r="D1" s="34"/>
       <c r="E1" s="27" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>499</v>
+        <v>442</v>
       </c>
       <c r="G1"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="35"/>
+      <c r="A2" s="36"/>
       <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
@@ -22949,7 +22438,7 @@
         <v>261</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="F3" s="16">
         <v>0</v>
@@ -22973,7 +22462,7 @@
         <v>261</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="F4" s="16">
         <v>0</v>
@@ -22997,7 +22486,7 @@
         <v>261</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="F5" s="16">
         <v>0</v>
@@ -23021,7 +22510,7 @@
         <v>261</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="F6" s="16">
         <v>0</v>
@@ -23045,7 +22534,7 @@
         <v>261</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="F7" s="16">
         <v>0</v>
@@ -23069,7 +22558,7 @@
         <v>261</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="F8" s="16">
         <v>0</v>
@@ -23093,7 +22582,7 @@
         <v>261</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="F9" s="16">
         <v>0</v>
@@ -23117,7 +22606,7 @@
         <v>261</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="F10" s="16">
         <v>0</v>
@@ -23141,7 +22630,7 @@
         <v>261</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="F11" s="16">
         <v>0</v>
@@ -23165,7 +22654,7 @@
         <v>261</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="F12" s="16">
         <v>0</v>
@@ -23189,7 +22678,7 @@
         <v>261</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="F13" s="16">
         <v>0</v>
@@ -23210,7 +22699,7 @@
         <v>260</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>5</v>
@@ -23258,10 +22747,10 @@
         <v>260</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="F16" s="16">
         <v>0</v>
@@ -23282,10 +22771,10 @@
         <v>260</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="F17" s="16">
         <v>0</v>
@@ -23306,10 +22795,10 @@
         <v>260</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="F18" s="16">
         <v>0</v>
@@ -23330,10 +22819,10 @@
         <v>260</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="F19" s="16">
         <v>0</v>
@@ -23354,10 +22843,10 @@
         <v>260</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="F20" s="16">
         <v>0</v>
@@ -23378,10 +22867,10 @@
         <v>260</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="F21" s="16">
         <v>0</v>
@@ -23402,7 +22891,7 @@
         <v>260</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>5</v>
@@ -23426,10 +22915,10 @@
         <v>260</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="F23" s="16">
         <v>0</v>
@@ -23450,10 +22939,10 @@
         <v>260</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="F24" s="16">
         <v>0</v>
@@ -23474,10 +22963,10 @@
         <v>260</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="F25" s="16">
         <v>0</v>
@@ -23498,10 +22987,10 @@
         <v>260</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="F26" s="16">
         <v>0</v>
@@ -23522,10 +23011,10 @@
         <v>260</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="F27" s="16">
         <v>0</v>
@@ -23546,10 +23035,10 @@
         <v>260</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="F28" s="16">
         <v>0</v>
@@ -23570,10 +23059,10 @@
         <v>260</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="F29" s="16">
         <v>0</v>
@@ -23594,10 +23083,10 @@
         <v>260</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="F30" s="16">
         <v>0</v>
@@ -23642,10 +23131,10 @@
         <v>260</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="F32" s="16">
         <v>0</v>
@@ -23858,10 +23347,10 @@
         <v>260</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="F41" s="16">
         <v>0</v>
@@ -23882,7 +23371,7 @@
         <v>260</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E42" s="30" t="s">
         <v>5</v>
@@ -23906,7 +23395,7 @@
         <v>260</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>172</v>
@@ -23930,7 +23419,7 @@
         <v>260</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>5</v>
@@ -23954,10 +23443,10 @@
         <v>260</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="F45" s="16">
         <v>0</v>
@@ -23978,10 +23467,10 @@
         <v>260</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="F46" s="16">
         <v>0</v>
@@ -24002,7 +23491,7 @@
         <v>260</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>169</v>
@@ -24026,7 +23515,7 @@
         <v>260</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>118</v>
@@ -24050,10 +23539,10 @@
         <v>260</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="F49" s="16">
         <v>0</v>
@@ -24074,10 +23563,10 @@
         <v>260</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="F50" s="16">
         <v>0</v>
@@ -24098,10 +23587,10 @@
         <v>260</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="F51" s="16">
         <v>0</v>
@@ -24122,7 +23611,7 @@
         <v>260</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>51</v>
@@ -24146,7 +23635,7 @@
         <v>260</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>169</v>
@@ -24170,7 +23659,7 @@
         <v>260</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>5</v>
@@ -24194,10 +23683,10 @@
         <v>260</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="F55" s="16">
         <v>0</v>
@@ -24218,7 +23707,7 @@
         <v>260</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>5</v>
@@ -24242,10 +23731,10 @@
         <v>260</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="F57" s="16">
         <v>0</v>
@@ -24266,10 +23755,10 @@
         <v>260</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F58" s="16">
         <v>0</v>
@@ -24290,10 +23779,10 @@
         <v>260</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F59" s="16">
         <v>0</v>
@@ -24314,10 +23803,10 @@
         <v>260</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="F60" s="16">
         <v>0</v>
@@ -24334,7 +23823,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F13 F32 F56:F58 F60 F43:F50 F17:F30 F52:F54">
-    <cfRule type="containsText" dxfId="11" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24351,7 +23840,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41">
-    <cfRule type="containsText" dxfId="10" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F41))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24368,7 +23857,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="containsText" dxfId="9" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F14))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24385,7 +23874,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="containsText" dxfId="8" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F15))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24402,7 +23891,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="containsText" dxfId="7" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F31))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24419,7 +23908,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42">
-    <cfRule type="containsText" dxfId="6" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F42))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24436,7 +23925,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="containsText" dxfId="5" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24453,7 +23942,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="containsText" dxfId="4" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F59))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24470,7 +23959,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33 F35 F37 F39">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F33))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24487,7 +23976,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34 F36 F38 F40">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24504,7 +23993,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24521,7 +24010,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F51))))</formula>
     </cfRule>
   </conditionalFormatting>
